--- a/artfynd/A 42502-2024 artfynd.xlsx
+++ b/artfynd/A 42502-2024 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120591271</v>
+        <v>120584930</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,31 +911,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628867</v>
+        <v>628541</v>
       </c>
       <c r="R4" t="n">
-        <v>7288246</v>
+        <v>7288710</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,17 +980,13 @@
           <t>2024-10-17</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>bohål i gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120584930</v>
+        <v>120585171</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,27 +1021,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1057,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628541</v>
+        <v>628558</v>
       </c>
       <c r="R5" t="n">
-        <v>7288710</v>
+        <v>7288689</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120585171</v>
+        <v>120590193</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,30 +1131,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628558</v>
+        <v>628781</v>
       </c>
       <c r="R6" t="n">
-        <v>7288689</v>
+        <v>7288467</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,13 +1201,17 @@
           <t>2024-10-17</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120590193</v>
+        <v>120591271</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1268,7 +1268,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628781</v>
+        <v>628867</v>
       </c>
       <c r="R7" t="n">
-        <v>7288467</v>
+        <v>7288246</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>bohål i gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2340,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120590232</v>
+        <v>120591365</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,31 +2356,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2388,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628803</v>
+        <v>628813</v>
       </c>
       <c r="R17" t="n">
-        <v>7288492</v>
+        <v>7288178</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,17 +2425,13 @@
           <t>2024-10-17</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2455,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120588693</v>
+        <v>120590232</v>
       </c>
       <c r="B18" t="n">
-        <v>90594</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2471,30 +2466,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2502,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628692</v>
+        <v>628803</v>
       </c>
       <c r="R18" t="n">
-        <v>7288441</v>
+        <v>7288492</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,13 +2536,17 @@
           <t>2024-10-17</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120591365</v>
+        <v>120588693</v>
       </c>
       <c r="B19" t="n">
-        <v>90576</v>
+        <v>90594</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2581,21 +2581,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628813</v>
+        <v>628692</v>
       </c>
       <c r="R19" t="n">
-        <v>7288178</v>
+        <v>7288441</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -5100,10 +5100,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120590308</v>
+        <v>120591238</v>
       </c>
       <c r="B42" t="n">
-        <v>90864</v>
+        <v>90598</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5116,21 +5116,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628853</v>
+        <v>628841</v>
       </c>
       <c r="R42" t="n">
-        <v>7288470</v>
+        <v>7288314</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5210,10 +5210,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120591238</v>
+        <v>120591352</v>
       </c>
       <c r="B43" t="n">
-        <v>90598</v>
+        <v>78624</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5226,27 +5226,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628841</v>
+        <v>628914</v>
       </c>
       <c r="R43" t="n">
-        <v>7288314</v>
+        <v>7288166</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120591352</v>
+        <v>120590308</v>
       </c>
       <c r="B44" t="n">
-        <v>78624</v>
+        <v>90864</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5336,27 +5336,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628914</v>
+        <v>628853</v>
       </c>
       <c r="R44" t="n">
-        <v>7288166</v>
+        <v>7288470</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -9204,10 +9204,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120587614</v>
+        <v>120590389</v>
       </c>
       <c r="B79" t="n">
-        <v>82321</v>
+        <v>57473</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9220,30 +9220,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9251,10 +9252,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>628666</v>
+        <v>628784</v>
       </c>
       <c r="R79" t="n">
-        <v>7288566</v>
+        <v>7288576</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9289,13 +9290,17 @@
           <t>2024-10-17</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Bohål i död björk</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9314,10 +9319,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120590389</v>
+        <v>120590317</v>
       </c>
       <c r="B80" t="n">
-        <v>57473</v>
+        <v>90598</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9330,31 +9335,30 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9362,10 +9366,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>628784</v>
+        <v>628853</v>
       </c>
       <c r="R80" t="n">
-        <v>7288576</v>
+        <v>7288470</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9400,17 +9404,13 @@
           <t>2024-10-17</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Bohål i död björk</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9429,10 +9429,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120590317</v>
+        <v>120587614</v>
       </c>
       <c r="B81" t="n">
-        <v>90598</v>
+        <v>82321</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9445,21 +9445,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9476,10 +9476,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>628853</v>
+        <v>628666</v>
       </c>
       <c r="R81" t="n">
-        <v>7288470</v>
+        <v>7288566</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>

--- a/artfynd/A 42502-2024 artfynd.xlsx
+++ b/artfynd/A 42502-2024 artfynd.xlsx
@@ -8217,7 +8217,7 @@
         <v>120591315</v>
       </c>
       <c r="B70" t="n">
-        <v>57975</v>
+        <v>57985</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 42502-2024 artfynd.xlsx
+++ b/artfynd/A 42502-2024 artfynd.xlsx
@@ -8217,11 +8217,11 @@
         <v>120591315</v>
       </c>
       <c r="B70" t="n">
-        <v>58003</v>
+        <v>58008</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8231,11 +8231,6 @@
       </c>
       <c r="E70" t="n">
         <v>102125</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Tallbit</t>
-        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>

--- a/artfynd/A 42502-2024 artfynd.xlsx
+++ b/artfynd/A 42502-2024 artfynd.xlsx
@@ -8217,7 +8217,7 @@
         <v>120591315</v>
       </c>
       <c r="B70" t="n">
-        <v>58008</v>
+        <v>58012</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8231,6 +8231,11 @@
       </c>
       <c r="E70" t="n">
         <v>102125</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>

--- a/artfynd/A 42502-2024 artfynd.xlsx
+++ b/artfynd/A 42502-2024 artfynd.xlsx
@@ -8217,7 +8217,7 @@
         <v>120591315</v>
       </c>
       <c r="B70" t="n">
-        <v>58012</v>
+        <v>58013</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
